--- a/414-rc---contact/ig/ValueSet-tddui-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-relation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:50:42+00:00</t>
+    <t>2026-01-28T14:07:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/ValueSet-tddui-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-relation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:07:57+00:00</t>
+    <t>2026-01-29T08:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
